--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4536-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4536-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7A35E75-42A1-470D-9831-B32A60251CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96933BC2-658A-4C55-A86A-2861CA65F77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E1B60A41-6ECA-42FC-8046-2F5DF798DEFC}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{252A43AD-861E-48AE-A2E3-BEF0413B2F33}"/>
   </bookViews>
   <sheets>
     <sheet name="4536-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1478,20 +1478,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2C8DC0-FD59-4BED-9EDE-22590EB107F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D94061-5EC0-47F0-AF10-5F804A50F113}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1519,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1549,7 +1549,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1645,7 +1645,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2021</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2020</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2019</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2018</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2017</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2016</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2015</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2014</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2013</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2012</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39" t="s">
         <v>45</v>
       </c>
